--- a/_qa/007_Model_Tests.xlsx
+++ b/_qa/007_Model_Tests.xlsx
@@ -8,8 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_source\Greenshoes\quodsi_lucidchart_package\_qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D440B1B-E35A-4B09-A0F1-586521873D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="10"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab Navigation" sheetId="1" r:id="rId1"/>
@@ -24,12 +25,12 @@
     <sheet name="Utilities" sheetId="10" r:id="rId10"/>
     <sheet name="Save-Cancel" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="429">
   <si>
     <t>Test ID</t>
   </si>
@@ -79,18 +80,6 @@
     <t>P1</t>
   </si>
   <si>
-    <t>Navigate to Basic tab</t>
-  </si>
-  <si>
-    <t>Model selected</t>
-  </si>
-  <si>
-    <t>Click Basic Settings icon</t>
-  </si>
-  <si>
-    <t>Basic Settings content displays</t>
-  </si>
-  <si>
     <t>MOD-NAV-002</t>
   </si>
   <si>
@@ -100,114 +89,54 @@
     <t>Navigate to States tab</t>
   </si>
   <si>
-    <t>Click States icon</t>
-  </si>
-  <si>
-    <t>States editor displays</t>
-  </si>
-  <si>
     <t>MOD-NAV-003</t>
   </si>
   <si>
     <t>Navigate to Requirements tab</t>
   </si>
   <si>
-    <t>Click Requirements icon</t>
-  </si>
-  <si>
-    <t>Resource Requirements manager displays</t>
-  </si>
-  <si>
     <t>MOD-NAV-004</t>
   </si>
   <si>
     <t>Navigate to Scenarios tab</t>
   </si>
   <si>
-    <t>Click Scenarios icon</t>
-  </si>
-  <si>
-    <t>Scenarios panel displays</t>
-  </si>
-  <si>
     <t>MOD-NAV-005</t>
   </si>
   <si>
     <t>Navigate to Validation tab</t>
   </si>
   <si>
-    <t>Click Validation icon</t>
-  </si>
-  <si>
-    <t>Validation dashboard displays</t>
-  </si>
-  <si>
     <t>MOD-NAV-006</t>
   </si>
   <si>
     <t>Navigate to Utilities tab</t>
   </si>
   <si>
-    <t>Click Utilities icon</t>
-  </si>
-  <si>
-    <t>Utilities panel displays</t>
-  </si>
-  <si>
     <t>MOD-NAV-007</t>
   </si>
   <si>
     <t>All tabs visible</t>
   </si>
   <si>
-    <t>Observe tab bar</t>
-  </si>
-  <si>
-    <t>All 6 tab icons visible</t>
-  </si>
-  <si>
     <t>MOD-NAV-008</t>
   </si>
   <si>
     <t>Tab tooltips display</t>
   </si>
   <si>
-    <t>Hover over each tab icon</t>
-  </si>
-  <si>
-    <t>Tooltip shows tab description</t>
-  </si>
-  <si>
     <t>MOD-SYNC-001</t>
   </si>
   <si>
     <t>Model data loads correctly</t>
   </si>
   <si>
-    <t>Model exists</t>
-  </si>
-  <si>
-    <t>Select model in panel</t>
-  </si>
-  <si>
-    <t>Form loads with model data</t>
-  </si>
-  <si>
     <t>MOD-SYNC-002</t>
   </si>
   <si>
     <t>Switch with unsaved changes</t>
   </si>
   <si>
-    <t>Changes made, not saved</t>
-  </si>
-  <si>
-    <t>Select different element, return to model</t>
-  </si>
-  <si>
-    <t>Changes auto-discarded</t>
-  </si>
-  <si>
     <t>MOD-SYNC-003</t>
   </si>
   <si>
@@ -217,895 +146,390 @@
     <t>External update sync</t>
   </si>
   <si>
-    <t>Collaborative editing</t>
-  </si>
-  <si>
-    <t>Another user updates model</t>
-  </si>
-  <si>
-    <t>Form reflects latest data</t>
-  </si>
-  <si>
     <t>MOD-EDGE-001</t>
   </si>
   <si>
     <t>Invalid model data</t>
   </si>
   <si>
-    <t>Corrupt model</t>
-  </si>
-  <si>
-    <t>Open editor with missing ID</t>
-  </si>
-  <si>
-    <t>Error message displayed gracefully</t>
-  </si>
-  <si>
     <t>MOD-EDGE-002</t>
   </si>
   <si>
     <t>Very long model name</t>
   </si>
   <si>
-    <t>Basic tab open</t>
-  </si>
-  <si>
-    <t>Enter 500+ character name</t>
-  </si>
-  <si>
-    <t>Handles gracefully</t>
-  </si>
-  <si>
     <t>MOD-EDGE-003</t>
   </si>
   <si>
     <t>Very large replications</t>
   </si>
   <si>
-    <t>Advanced expanded</t>
-  </si>
-  <si>
-    <t>Enter 999999 in replications</t>
-  </si>
-  <si>
-    <t>Handles or validates appropriately</t>
-  </si>
-  <si>
     <t>MOD-EDGE-004</t>
   </si>
   <si>
     <t>Zero run time</t>
   </si>
   <si>
-    <t>Clock mode</t>
-  </si>
-  <si>
-    <t>Enter 0 in Run Time field</t>
-  </si>
-  <si>
-    <t>Accepts 0 or shows validation</t>
-  </si>
-  <si>
     <t>MOD-EDGE-005</t>
   </si>
   <si>
     <t>Browser refresh during edit</t>
   </si>
   <si>
-    <t>Make changes, refresh browser</t>
-  </si>
-  <si>
-    <t>Changes are lost (expected)</t>
-  </si>
-  <si>
     <t>MOD-EDGE-006</t>
   </si>
   <si>
     <t>Default random seed</t>
   </si>
   <si>
-    <t>New model</t>
-  </si>
-  <si>
-    <t>Observe default seed value</t>
-  </si>
-  <si>
-    <t>Default seed is 12345</t>
-  </si>
-  <si>
     <t>MOD-BASIC-001</t>
   </si>
   <si>
     <t>Edit model name</t>
   </si>
   <si>
-    <t>Type new name in Model Name field</t>
-  </si>
-  <si>
-    <t>Name updates, Save button enables</t>
-  </si>
-  <si>
     <t>MOD-BASIC-002</t>
   </si>
   <si>
     <t>Edit run time value</t>
   </si>
   <si>
-    <t>Basic tab, Clock mode</t>
-  </si>
-  <si>
-    <t>Enter 100 in Run Time field</t>
-  </si>
-  <si>
-    <t>Value updates to 100</t>
-  </si>
-  <si>
     <t>MOD-BASIC-003</t>
   </si>
   <si>
     <t>Change run time unit</t>
   </si>
   <si>
-    <t>Select Days from Run Time unit dropdown</t>
-  </si>
-  <si>
-    <t>Unit changes to Days</t>
-  </si>
-  <si>
     <t>MOD-BASIC-004</t>
   </si>
   <si>
     <t>Run time hidden in Calendar mode</t>
   </si>
   <si>
-    <t>Basic tab, Calendar Date mode</t>
-  </si>
-  <si>
-    <t>Observe Run Time section</t>
-  </si>
-  <si>
-    <t>Run Time field not visible</t>
-  </si>
-  <si>
     <t>MOD-BASIC-005</t>
   </si>
   <si>
     <t>Expand Advanced Settings</t>
   </si>
   <si>
-    <t>Click Advanced Settings accordion</t>
-  </si>
-  <si>
-    <t>Accordion expands showing advanced fields</t>
-  </si>
-  <si>
     <t>MOD-BASIC-006</t>
   </si>
   <si>
     <t>Collapse Advanced Settings</t>
   </si>
   <si>
-    <t>Advanced Settings expanded</t>
-  </si>
-  <si>
-    <t>Accordion collapses</t>
-  </si>
-  <si>
     <t>MOD-BASIC-007</t>
   </si>
   <si>
     <t>Edit replications</t>
   </si>
   <si>
-    <t>Enter 10 in Replications field</t>
-  </si>
-  <si>
-    <t>Value updates to 10</t>
-  </si>
-  <si>
     <t>MOD-BASIC-008</t>
   </si>
   <si>
     <t>Minimum replications</t>
   </si>
   <si>
-    <t>Enter 0 in Replications field</t>
-  </si>
-  <si>
-    <t>Value defaults to 1 or shows warning</t>
-  </si>
-  <si>
     <t>MOD-BASIC-009</t>
   </si>
   <si>
     <t>Change time mode to Calendar</t>
   </si>
   <si>
-    <t>Select CalendarDate from Time Mode</t>
-  </si>
-  <si>
-    <t>Date fields appear, clock fields hidden</t>
-  </si>
-  <si>
     <t>MOD-BASIC-010</t>
   </si>
   <si>
     <t>Change time mode to Clock</t>
   </si>
   <si>
-    <t>Advanced Settings, Calendar mode</t>
-  </si>
-  <si>
-    <t>Select Clock from Time Mode</t>
-  </si>
-  <si>
-    <t>Clock fields appear, date fields hidden</t>
-  </si>
-  <si>
     <t>MOD-BASIC-011</t>
   </si>
   <si>
     <t>Edit clock unit</t>
   </si>
   <si>
-    <t>Clock mode, Advanced expanded</t>
-  </si>
-  <si>
-    <t>Select Minutes from Clock Unit</t>
-  </si>
-  <si>
-    <t>Clock unit changes to Minutes</t>
-  </si>
-  <si>
     <t>MOD-BASIC-012</t>
   </si>
   <si>
     <t>Edit warmup time</t>
   </si>
   <si>
-    <t>Enter 10 in Warmup Time</t>
-  </si>
-  <si>
-    <t>Warmup time updates to 10</t>
-  </si>
-  <si>
     <t>MOD-CAL-001</t>
   </si>
   <si>
     <t>Set start date</t>
   </si>
   <si>
-    <t>Calendar Date mode</t>
-  </si>
-  <si>
-    <t>Enter start date using datetime picker</t>
-  </si>
-  <si>
-    <t>Start date updates</t>
-  </si>
-  <si>
     <t>MOD-CAL-002</t>
   </si>
   <si>
     <t>Set finish date</t>
   </si>
   <si>
-    <t>Enter finish date using datetime picker</t>
-  </si>
-  <si>
-    <t>Finish date updates</t>
-  </si>
-  <si>
     <t>MOD-CAL-003</t>
   </si>
   <si>
     <t>Set warmup date</t>
   </si>
   <si>
-    <t>Enter warmup date using datetime picker</t>
-  </si>
-  <si>
-    <t>Warmup date updates</t>
-  </si>
-  <si>
     <t>MOD-CAL-004</t>
   </si>
   <si>
     <t>Clear start date</t>
   </si>
   <si>
-    <t>Calendar Date mode, date set</t>
-  </si>
-  <si>
-    <t>Clear the start date field</t>
-  </si>
-  <si>
-    <t>Date clears to empty</t>
-  </si>
-  <si>
     <t>MOD-CAL-005</t>
   </si>
   <si>
     <t>Finish before start validation</t>
   </si>
   <si>
-    <t>Set finish date before start date</t>
-  </si>
-  <si>
-    <t>Validation warning or error</t>
-  </si>
-  <si>
     <t>MOD-CAL-006</t>
   </si>
   <si>
     <t>Warmup outside range</t>
   </si>
   <si>
-    <t>Set warmup before start date</t>
-  </si>
-  <si>
     <t>MOD-CAL-007</t>
   </si>
   <si>
     <t>Date info tooltips</t>
   </si>
   <si>
-    <t>Hover over date field info icons</t>
-  </si>
-  <si>
-    <t>Tooltips explain each date field</t>
-  </si>
-  <si>
     <t>MOD-STATE-001</t>
   </si>
   <si>
     <t>Add new state</t>
   </si>
   <si>
-    <t>States tab open</t>
-  </si>
-  <si>
-    <t>Click add state in States editor</t>
-  </si>
-  <si>
-    <t>New state added to list</t>
-  </si>
-  <si>
     <t>MOD-STATE-002</t>
   </si>
   <si>
     <t>Edit state name</t>
   </si>
   <si>
-    <t>State exists</t>
-  </si>
-  <si>
-    <t>Change state name</t>
-  </si>
-  <si>
-    <t>State name updates</t>
-  </si>
-  <si>
     <t>MOD-STATE-003</t>
   </si>
   <si>
     <t>Delete state</t>
   </si>
   <si>
-    <t>Remove a state</t>
-  </si>
-  <si>
-    <t>State removed from list</t>
-  </si>
-  <si>
     <t>MOD-STATE-004</t>
   </si>
   <si>
     <t>States auto-save</t>
   </si>
   <si>
-    <t>Make change to state</t>
-  </si>
-  <si>
-    <t>Saves immediately (no Save button)</t>
-  </si>
-  <si>
     <t>MOD-REQ-001</t>
   </si>
   <si>
     <t>Add new requirement</t>
   </si>
   <si>
-    <t>Requirements tab open</t>
-  </si>
-  <si>
-    <t>Click Add button</t>
-  </si>
-  <si>
-    <t>Requirement modal opens</t>
-  </si>
-  <si>
     <t>MOD-REQ-002</t>
   </si>
   <si>
     <t>Save new requirement</t>
   </si>
   <si>
-    <t>Modal open, filled out</t>
-  </si>
-  <si>
-    <t>Enter name, configure resources, click Save</t>
-  </si>
-  <si>
-    <t>Requirement added to list</t>
-  </si>
-  <si>
     <t>MOD-REQ-003</t>
   </si>
   <si>
     <t>Edit existing requirement</t>
   </si>
   <si>
-    <t>Requirement exists</t>
-  </si>
-  <si>
-    <t>Click Edit on requirement</t>
-  </si>
-  <si>
-    <t>Modal opens with requirement data</t>
-  </si>
-  <si>
     <t>MOD-REQ-004</t>
   </si>
   <si>
     <t>Delete requirement</t>
   </si>
   <si>
-    <t>Requirement exists, unused</t>
-  </si>
-  <si>
-    <t>Click Delete on requirement</t>
-  </si>
-  <si>
-    <t>Requirement removed from list</t>
-  </si>
-  <si>
     <t>MOD-REQ-005</t>
   </si>
   <si>
     <t>Delete requirement in use</t>
   </si>
   <si>
-    <t>Requirement used by actions</t>
-  </si>
-  <si>
-    <t>Click Delete on used requirement</t>
-  </si>
-  <si>
-    <t>Shows usage count warning</t>
-  </si>
-  <si>
     <t>MOD-REQ-006</t>
   </si>
   <si>
     <t>Cancel modal without saving</t>
   </si>
   <si>
-    <t>Modal open with changes</t>
-  </si>
-  <si>
-    <t>Click Cancel or close modal</t>
-  </si>
-  <si>
-    <t>Changes discarded, modal closes</t>
-  </si>
-  <si>
     <t>MOD-REQ-007</t>
   </si>
   <si>
     <t>Requirements auto-save</t>
   </si>
   <si>
-    <t>Requirements tab</t>
-  </si>
-  <si>
-    <t>Make change via modal</t>
-  </si>
-  <si>
-    <t>Saves immediately after modal close</t>
-  </si>
-  <si>
     <t>MOD-REQ-008</t>
   </si>
   <si>
     <t>Auto-generated requirements shown</t>
   </si>
   <si>
-    <t>Resources exist in model</t>
-  </si>
-  <si>
-    <t>Open Requirements tab</t>
-  </si>
-  <si>
-    <t>Auto-generated requirements visible</t>
-  </si>
-  <si>
     <t>MOD-REQ-009</t>
   </si>
   <si>
     <t>Edit auto-generated requirement</t>
   </si>
   <si>
-    <t>Auto-generated req exists</t>
-  </si>
-  <si>
-    <t>Click Edit on auto-generated</t>
-  </si>
-  <si>
-    <t>Modal opens, can customize</t>
-  </si>
-  <si>
     <t>MOD-REQ-010</t>
   </si>
   <si>
     <t>Empty requirements list</t>
   </si>
   <si>
-    <t>No resources in model</t>
-  </si>
-  <si>
-    <t>Empty state or message shown</t>
-  </si>
-  <si>
     <t>MOD-SCEN-001</t>
   </si>
   <si>
     <t>View scenarios panel</t>
   </si>
   <si>
-    <t>Scenarios tab selected</t>
-  </si>
-  <si>
-    <t>Observe Scenarios panel</t>
-  </si>
-  <si>
-    <t>Scenarios panel displays correctly</t>
-  </si>
-  <si>
     <t>MOD-SCEN-002</t>
   </si>
   <si>
     <t>Create new scenario</t>
   </si>
   <si>
-    <t>Scenarios tab open</t>
-  </si>
-  <si>
-    <t>Click create scenario button</t>
-  </si>
-  <si>
-    <t>New scenario created</t>
-  </si>
-  <si>
     <t>MOD-SCEN-003</t>
   </si>
   <si>
     <t>Edit scenario settings</t>
   </si>
   <si>
-    <t>Scenario exists</t>
-  </si>
-  <si>
-    <t>Modify scenario parameters</t>
-  </si>
-  <si>
-    <t>Changes saved</t>
-  </si>
-  <si>
     <t>MOD-SCEN-004</t>
   </si>
   <si>
     <t>Delete scenario</t>
   </si>
   <si>
-    <t>Delete the scenario</t>
-  </si>
-  <si>
-    <t>Scenario removed</t>
-  </si>
-  <si>
     <t>MOD-SCEN-005</t>
   </si>
   <si>
     <t>Scenarios auto-save</t>
   </si>
   <si>
-    <t>Scenarios tab</t>
-  </si>
-  <si>
-    <t>Make change to scenario</t>
-  </si>
-  <si>
-    <t>Saves immediately</t>
-  </si>
-  <si>
     <t>MOD-SCEN-006</t>
   </si>
   <si>
     <t>Multiple scenarios</t>
   </si>
   <si>
-    <t>Multiple scenarios exist</t>
-  </si>
-  <si>
-    <t>View scenario list</t>
-  </si>
-  <si>
-    <t>All scenarios listed correctly</t>
-  </si>
-  <si>
     <t>MOD-VAL-001</t>
   </si>
   <si>
     <t>Validation auto-triggers</t>
   </si>
   <si>
-    <t>Model has issues</t>
-  </si>
-  <si>
-    <t>Click Validation tab</t>
-  </si>
-  <si>
-    <t>Validation runs automatically</t>
-  </si>
-  <si>
     <t>MOD-VAL-002</t>
   </si>
   <si>
     <t>View validation errors</t>
   </si>
   <si>
-    <t>Model has errors</t>
-  </si>
-  <si>
-    <t>Errors displayed in dashboard</t>
-  </si>
-  <si>
     <t>MOD-VAL-003</t>
   </si>
   <si>
     <t>View validation warnings</t>
   </si>
   <si>
-    <t>Model has warnings</t>
-  </si>
-  <si>
-    <t>Warnings displayed in dashboard</t>
-  </si>
-  <si>
     <t>MOD-VAL-004</t>
   </si>
   <si>
     <t>Valid model state</t>
   </si>
   <si>
-    <t>Model is valid</t>
-  </si>
-  <si>
-    <t>Success message or empty error list</t>
-  </si>
-  <si>
     <t>MOD-VAL-005</t>
   </si>
   <si>
     <t>Click validation item</t>
   </si>
   <si>
-    <t>Validation error exists</t>
-  </si>
-  <si>
-    <t>Click on error item</t>
-  </si>
-  <si>
-    <t>Navigates to or highlights problem element</t>
-  </si>
-  <si>
     <t>MOD-VAL-006</t>
   </si>
   <si>
     <t>Error count badge</t>
   </si>
   <si>
-    <t>Observe Validation tab icon</t>
-  </si>
-  <si>
-    <t>Badge shows error count</t>
-  </si>
-  <si>
     <t>MOD-VAL-007</t>
   </si>
   <si>
     <t>Validation refresh</t>
   </si>
   <si>
-    <t>Validation tab open</t>
-  </si>
-  <si>
-    <t>Make model change, return to Validation</t>
-  </si>
-  <si>
-    <t>Validation results update</t>
-  </si>
-  <si>
     <t>MOD-UTIL-001</t>
   </si>
   <si>
     <t>View Model JSON button</t>
   </si>
   <si>
-    <t>Utilities tab open</t>
-  </si>
-  <si>
-    <t>Observe Diagnostics section</t>
-  </si>
-  <si>
-    <t>View Model JSON button visible</t>
-  </si>
-  <si>
     <t>MOD-UTIL-002</t>
   </si>
   <si>
     <t>Click View Model JSON</t>
   </si>
   <si>
-    <t>Click View Model JSON button</t>
-  </si>
-  <si>
-    <t>Modal opens with model JSON</t>
-  </si>
-  <si>
     <t>MOD-UTIL-003</t>
   </si>
   <si>
     <t>Close JSON viewer</t>
   </si>
   <si>
-    <t>JSON viewer modal open</t>
-  </si>
-  <si>
-    <t>Click close or outside modal</t>
-  </si>
-  <si>
-    <t>Modal closes</t>
-  </si>
-  <si>
     <t>MOD-UTIL-004</t>
   </si>
   <si>
     <t>JSON content valid</t>
   </si>
   <si>
-    <t>JSON viewer open</t>
-  </si>
-  <si>
-    <t>Inspect JSON content</t>
-  </si>
-  <si>
-    <t>JSON is well-formed and readable</t>
-  </si>
-  <si>
     <t>MOD-SAVE-001</t>
   </si>
   <si>
     <t>Save button initially disabled</t>
   </si>
   <si>
-    <t>Model just selected</t>
-  </si>
-  <si>
-    <t>Open model with no changes</t>
-  </si>
-  <si>
-    <t>Save button is disabled/grayed</t>
-  </si>
-  <si>
     <t>MOD-SAVE-002</t>
   </si>
   <si>
     <t>Save button enables on change</t>
   </si>
   <si>
-    <t>Model selected, Basic tab</t>
-  </si>
-  <si>
-    <t>Make any change to basic fields</t>
-  </si>
-  <si>
-    <t>Save button becomes enabled</t>
-  </si>
-  <si>
     <t>MOD-SAVE-003</t>
   </si>
   <si>
     <t>Save persists changes</t>
   </si>
   <si>
-    <t>Changes made</t>
-  </si>
-  <si>
-    <t>Make change, click Save</t>
-  </si>
-  <si>
-    <t>Changes saved, Save button disables</t>
-  </si>
-  <si>
     <t>MOD-SAVE-004</t>
   </si>
   <si>
     <t>Cancel discards changes</t>
   </si>
   <si>
-    <t>Make changes, click Cancel</t>
-  </si>
-  <si>
-    <t>Form resets to original values</t>
-  </si>
-  <si>
     <t>MOD-SAVE-005</t>
   </si>
   <si>
     <t>Dirty state tracking</t>
   </si>
   <si>
-    <t>Make change, switch tabs, return to Basic</t>
-  </si>
-  <si>
-    <t>Changes still present</t>
-  </si>
-  <si>
     <t>MOD-SAVE-006</t>
   </si>
   <si>
     <t>Save shows loading state</t>
   </si>
   <si>
-    <t>Click Save button</t>
-  </si>
-  <si>
-    <t>Button shows 'Saving...' text</t>
-  </si>
-  <si>
     <t>MOD-SAVE-007</t>
   </si>
   <si>
     <t>Save/Cancel hidden on auto-save tabs</t>
   </si>
   <si>
-    <t>States/Requirements/Scenarios tab</t>
-  </si>
-  <si>
-    <t>Observe footer area</t>
-  </si>
-  <si>
-    <t>Save/Cancel buttons not shown</t>
-  </si>
-  <si>
     <t>MOD-VAL-008</t>
   </si>
   <si>
     <t>Generator no outgoing connectors error</t>
   </si>
   <si>
-    <t>Generator with no exit</t>
-  </si>
-  <si>
-    <t>1. Create generator with no outgoing connector
-2. Open Validation tab</t>
-  </si>
-  <si>
-    <t>ERROR: "Generator has no outgoing connectors. Entities cannot flow into the system."</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -1115,144 +539,52 @@
     <t>Generator no terminal path error</t>
   </si>
   <si>
-    <t>Generator exists</t>
-  </si>
-  <si>
-    <t>1. Create generator → activity loop with no terminal
-2. Open Validation tab</t>
-  </si>
-  <si>
-    <t>ERROR: "Generator has no path to a terminal Activity. All paths lead to dead-ends or loops without exits."</t>
-  </si>
-  <si>
     <t>MOD-VAL-010</t>
   </si>
   <si>
     <t>Generator dead-end path error</t>
   </si>
   <si>
-    <t>Generator with connected activities</t>
-  </si>
-  <si>
-    <t>1. Create generator → activity → activity (no outgoing)
-2. Middle activity has outgoing connector to nowhere
-3. Open Validation tab</t>
-  </si>
-  <si>
-    <t>ERROR: "Generator has paths that lead to non-terminal Activities with no exit. Entities may get stuck."</t>
-  </si>
-  <si>
     <t>MOD-VAL-011</t>
   </si>
   <si>
     <t>Valid path to terminal activity</t>
   </si>
   <si>
-    <t>Complete flow exists</t>
-  </si>
-  <si>
-    <t>1. Create generator → activity → activity (terminal)
-2. Open Validation tab</t>
-  </si>
-  <si>
-    <t>No path validation errors shown</t>
-  </si>
-  <si>
     <t>MOD-VAL-012</t>
   </si>
   <si>
     <t>Loop with valid exit path</t>
   </si>
   <si>
-    <t>Generator with loop</t>
-  </si>
-  <si>
-    <t>1. Create generator → A → B → A (loop)
-2. Add A → C (terminal)
-3. Open Validation tab</t>
-  </si>
-  <si>
-    <t>No path validation errors (loop has exit)</t>
-  </si>
-  <si>
     <t>MOD-VAL-013</t>
   </si>
   <si>
     <t>Multiple generators path validation</t>
   </si>
   <si>
-    <t>Multiple generators</t>
-  </si>
-  <si>
-    <t>1. Create two generators with different path issues
-2. Open Validation tab</t>
-  </si>
-  <si>
-    <t>Both generators show appropriate path validation errors</t>
-  </si>
-  <si>
     <t>MOD-VAL-014</t>
   </si>
   <si>
     <t>No generators defined error</t>
   </si>
   <si>
-    <t>Empty model or all generators deleted</t>
-  </si>
-  <si>
-    <t>1. Create model with no generators
-2. Open Validation tab</t>
-  </si>
-  <si>
-    <t>ERROR: "Model must have at least one generator" or similar</t>
-  </si>
-  <si>
     <t>MOD-VAL-015</t>
   </si>
   <si>
     <t>No activities defined error</t>
   </si>
   <si>
-    <t>Model with no activities</t>
-  </si>
-  <si>
-    <t>1. Create model with generator but no activities
-2. Open Validation tab</t>
-  </si>
-  <si>
-    <t>ERROR: "Model must have at least one activity" or similar</t>
-  </si>
-  <si>
     <t>MOD-VAL-016</t>
   </si>
   <si>
     <t>No entities defined error</t>
   </si>
   <si>
-    <t>Model with no entities</t>
-  </si>
-  <si>
-    <t>1. Delete all entities from model
-2. Open Validation tab</t>
-  </si>
-  <si>
-    <t>ERROR: "Model must have at least one entity" or similar</t>
-  </si>
-  <si>
     <t>MOD-VAL-017</t>
   </si>
   <si>
     <t>All required elements present</t>
-  </si>
-  <si>
-    <t>Complete model</t>
-  </si>
-  <si>
-    <t>1. Create model with generator, activity, and entity
-2. Open Validation tab</t>
-  </si>
-  <si>
-    <t>No element count errors shown</t>
   </si>
   <si>
     <t>Navigate to Basic Settings tab</t>
@@ -3002,19 +2334,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
     </font>
   </fonts>
   <fills count="2">
@@ -3037,17 +2370,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3060,7 +2397,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3345,24 +2682,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="13.21875"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="25.6640625"/>
-    <col bestFit="true" customWidth="true" max="4" min="4" width="13.5546875"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="21.6640625"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="35.21875"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3406,7 +2743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -3414,348 +2751,348 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>404</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>405</v>
+        <v>186</v>
       </c>
       <c r="E2" t="s">
-        <v>406</v>
+        <v>187</v>
       </c>
       <c r="F2" t="s">
-        <v>407</v>
+        <v>188</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K3" t="s">
+        <v>166</v>
+      </c>
+      <c r="L3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J4" t="s">
+        <v>166</v>
+      </c>
+      <c r="K4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4" t="s">
+        <v>166</v>
+      </c>
+      <c r="M4" t="s">
+        <v>166</v>
+      </c>
+      <c r="N4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
-        <v>408</v>
-      </c>
-      <c r="E3" t="s">
-        <v>409</v>
-      </c>
-      <c r="F3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H3" t="s">
-        <v>358</v>
-      </c>
-      <c r="I3" t="s">
-        <v>358</v>
-      </c>
-      <c r="J3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K3" t="s">
-        <v>358</v>
-      </c>
-      <c r="L3" t="s">
-        <v>358</v>
-      </c>
-      <c r="M3" t="s">
-        <v>358</v>
-      </c>
-      <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
+      <c r="D5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J5" t="s">
+        <v>166</v>
+      </c>
+      <c r="K5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L5" t="s">
+        <v>166</v>
+      </c>
+      <c r="M5" t="s">
+        <v>166</v>
+      </c>
+      <c r="N5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H6" t="s">
+        <v>166</v>
+      </c>
+      <c r="I6" t="s">
+        <v>166</v>
+      </c>
+      <c r="J6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K6" t="s">
+        <v>166</v>
+      </c>
+      <c r="L6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M6" t="s">
+        <v>166</v>
+      </c>
+      <c r="N6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="D4" t="s">
-        <v>408</v>
-      </c>
-      <c r="E4" t="s">
-        <v>411</v>
-      </c>
-      <c r="F4" t="s">
-        <v>412</v>
-      </c>
-      <c r="G4" t="s">
-        <v>358</v>
-      </c>
-      <c r="H4" t="s">
-        <v>358</v>
-      </c>
-      <c r="I4" t="s">
-        <v>358</v>
-      </c>
-      <c r="J4" t="s">
-        <v>358</v>
-      </c>
-      <c r="K4" t="s">
-        <v>358</v>
-      </c>
-      <c r="L4" t="s">
-        <v>358</v>
-      </c>
-      <c r="M4" t="s">
-        <v>358</v>
-      </c>
-      <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>408</v>
-      </c>
-      <c r="E5" t="s">
-        <v>413</v>
-      </c>
-      <c r="F5" t="s">
-        <v>414</v>
-      </c>
-      <c r="G5" t="s">
-        <v>358</v>
-      </c>
-      <c r="H5" t="s">
-        <v>358</v>
-      </c>
-      <c r="I5" t="s">
-        <v>358</v>
-      </c>
-      <c r="J5" t="s">
-        <v>358</v>
-      </c>
-      <c r="K5" t="s">
-        <v>358</v>
-      </c>
-      <c r="L5" t="s">
-        <v>358</v>
-      </c>
-      <c r="M5" t="s">
-        <v>358</v>
-      </c>
-      <c r="N5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>408</v>
-      </c>
-      <c r="E6" t="s">
-        <v>415</v>
-      </c>
-      <c r="F6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G6" t="s">
-        <v>358</v>
-      </c>
-      <c r="H6" t="s">
-        <v>358</v>
-      </c>
-      <c r="I6" t="s">
-        <v>358</v>
-      </c>
-      <c r="J6" t="s">
-        <v>358</v>
-      </c>
-      <c r="K6" t="s">
-        <v>358</v>
-      </c>
-      <c r="L6" t="s">
-        <v>358</v>
-      </c>
-      <c r="M6" t="s">
-        <v>358</v>
-      </c>
-      <c r="N6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>408</v>
+        <v>189</v>
       </c>
       <c r="E7" t="s">
-        <v>417</v>
+        <v>198</v>
       </c>
       <c r="F7" t="s">
-        <v>418</v>
+        <v>199</v>
       </c>
       <c r="G7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>419</v>
+        <v>200</v>
       </c>
       <c r="E8" t="s">
-        <v>420</v>
+        <v>201</v>
       </c>
       <c r="F8" t="s">
-        <v>421</v>
+        <v>202</v>
       </c>
       <c r="G8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N8" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>422</v>
+        <v>203</v>
       </c>
       <c r="E9" t="s">
-        <v>423</v>
+        <v>204</v>
       </c>
       <c r="F9" t="s">
-        <v>424</v>
+        <v>205</v>
       </c>
       <c r="G9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -3766,23 +3103,23 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="13.44140625"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="4" min="3" width="21.5546875"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="25.88671875"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="28.77734375"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3826,180 +3163,180 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>303</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>590</v>
+        <v>371</v>
       </c>
       <c r="E2" t="s">
-        <v>591</v>
+        <v>372</v>
       </c>
       <c r="F2" t="s">
-        <v>592</v>
+        <v>373</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>593</v>
+        <v>374</v>
       </c>
       <c r="E3" t="s">
-        <v>594</v>
+        <v>375</v>
       </c>
       <c r="F3" t="s">
-        <v>595</v>
+        <v>376</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>311</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>596</v>
+        <v>377</v>
       </c>
       <c r="E4" t="s">
-        <v>597</v>
+        <v>378</v>
       </c>
       <c r="F4" t="s">
-        <v>598</v>
+        <v>379</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>316</v>
+        <v>148</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>317</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>599</v>
+        <v>380</v>
       </c>
       <c r="E5" t="s">
-        <v>600</v>
+        <v>381</v>
       </c>
       <c r="F5" t="s">
-        <v>601</v>
+        <v>382</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -4010,24 +3347,24 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="13.77734375"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="32.44140625"/>
-    <col bestFit="true" customWidth="true" max="4" min="4" width="30.21875"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="35.21875"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="30.88671875"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4071,312 +3408,312 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>321</v>
+        <v>150</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>322</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>602</v>
+        <v>383</v>
       </c>
       <c r="E2" t="s">
-        <v>603</v>
+        <v>384</v>
       </c>
       <c r="F2" t="s">
-        <v>604</v>
+        <v>385</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>327</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>605</v>
+        <v>386</v>
       </c>
       <c r="E3" t="s">
-        <v>606</v>
+        <v>387</v>
       </c>
       <c r="F3" t="s">
-        <v>607</v>
+        <v>388</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>331</v>
+        <v>154</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>332</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>608</v>
+        <v>389</v>
       </c>
       <c r="E4" t="s">
-        <v>609</v>
+        <v>390</v>
       </c>
       <c r="F4" t="s">
-        <v>610</v>
+        <v>391</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>336</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>337</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
-        <v>611</v>
+        <v>392</v>
       </c>
       <c r="E5" t="s">
-        <v>612</v>
+        <v>393</v>
       </c>
       <c r="F5" t="s">
-        <v>613</v>
+        <v>394</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>340</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>341</v>
+        <v>159</v>
       </c>
       <c r="D6" t="s">
-        <v>614</v>
+        <v>395</v>
       </c>
       <c r="E6" t="s">
-        <v>615</v>
+        <v>396</v>
       </c>
       <c r="F6" t="s">
-        <v>616</v>
+        <v>397</v>
       </c>
       <c r="G6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>344</v>
+        <v>160</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>345</v>
+        <v>161</v>
       </c>
       <c r="D7" t="s">
-        <v>617</v>
+        <v>398</v>
       </c>
       <c r="E7" t="s">
-        <v>618</v>
+        <v>399</v>
       </c>
       <c r="F7" t="s">
-        <v>619</v>
+        <v>400</v>
       </c>
       <c r="G7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>348</v>
+        <v>162</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>163</v>
       </c>
       <c r="D8" t="s">
-        <v>522</v>
+        <v>303</v>
       </c>
       <c r="E8" t="s">
-        <v>620</v>
+        <v>401</v>
       </c>
       <c r="F8" t="s">
-        <v>621</v>
+        <v>402</v>
       </c>
       <c r="G8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -4387,24 +3724,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="14"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="24.77734375"/>
-    <col bestFit="true" customWidth="true" max="4" min="4" width="21.88671875"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="34.88671875"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="24"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4448,136 +3785,136 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>622</v>
+        <v>403</v>
       </c>
       <c r="E2" t="s">
-        <v>623</v>
+        <v>404</v>
       </c>
       <c r="F2" t="s">
-        <v>624</v>
+        <v>405</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>625</v>
+        <v>406</v>
       </c>
       <c r="E3" t="s">
-        <v>626</v>
+        <v>407</v>
       </c>
       <c r="F3" t="s">
-        <v>627</v>
+        <v>408</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>628</v>
+        <v>409</v>
       </c>
       <c r="E4" t="s">
-        <v>629</v>
+        <v>410</v>
       </c>
       <c r="F4" t="s">
-        <v>630</v>
+        <v>411</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -4588,24 +3925,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="14.109375"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="23.33203125"/>
-    <col bestFit="true" customWidth="true" max="4" min="4" width="21.88671875"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="26.77734375"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="29.33203125"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4649,268 +3986,268 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>631</v>
+        <v>412</v>
       </c>
       <c r="E2" t="s">
-        <v>632</v>
+        <v>413</v>
       </c>
       <c r="F2" t="s">
-        <v>633</v>
+        <v>414</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>614</v>
+        <v>395</v>
       </c>
       <c r="E3" t="s">
-        <v>634</v>
+        <v>415</v>
       </c>
       <c r="F3" t="s">
-        <v>635</v>
+        <v>416</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>636</v>
+        <v>417</v>
       </c>
       <c r="E4" t="s">
-        <v>637</v>
+        <v>418</v>
       </c>
       <c r="F4" t="s">
-        <v>638</v>
+        <v>419</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>639</v>
+        <v>420</v>
       </c>
       <c r="E5" t="s">
-        <v>640</v>
+        <v>421</v>
       </c>
       <c r="F5" t="s">
-        <v>641</v>
+        <v>422</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>642</v>
+        <v>423</v>
       </c>
       <c r="E6" t="s">
-        <v>643</v>
+        <v>424</v>
       </c>
       <c r="F6" t="s">
-        <v>644</v>
+        <v>425</v>
       </c>
       <c r="G6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>645</v>
+        <v>426</v>
       </c>
       <c r="E7" t="s">
-        <v>646</v>
+        <v>427</v>
       </c>
       <c r="F7" t="s">
-        <v>647</v>
+        <v>428</v>
       </c>
       <c r="G7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -4921,24 +4258,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="14.44140625"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="29.21875"/>
-    <col bestFit="true" customWidth="true" max="4" min="4" width="29.33203125"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="35.6640625"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="37.109375"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4982,532 +4319,532 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>425</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
-        <v>426</v>
+        <v>207</v>
       </c>
       <c r="F2" t="s">
-        <v>427</v>
+        <v>208</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>428</v>
+        <v>209</v>
       </c>
       <c r="E3" t="s">
-        <v>429</v>
+        <v>210</v>
       </c>
       <c r="F3" t="s">
-        <v>430</v>
+        <v>211</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>431</v>
+        <v>212</v>
       </c>
       <c r="E4" t="s">
-        <v>432</v>
+        <v>213</v>
       </c>
       <c r="F4" t="s">
-        <v>433</v>
+        <v>214</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>434</v>
+        <v>215</v>
       </c>
       <c r="E5" t="s">
-        <v>435</v>
+        <v>216</v>
       </c>
       <c r="F5" t="s">
-        <v>436</v>
+        <v>217</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>437</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
-        <v>438</v>
+        <v>219</v>
       </c>
       <c r="F6" t="s">
-        <v>439</v>
+        <v>220</v>
       </c>
       <c r="G6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>440</v>
+        <v>221</v>
       </c>
       <c r="E7" t="s">
-        <v>441</v>
+        <v>222</v>
       </c>
       <c r="F7" t="s">
-        <v>442</v>
+        <v>223</v>
       </c>
       <c r="G7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>443</v>
+        <v>224</v>
       </c>
       <c r="E8" t="s">
-        <v>444</v>
+        <v>225</v>
       </c>
       <c r="F8" t="s">
-        <v>445</v>
+        <v>226</v>
       </c>
       <c r="G8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N8" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>443</v>
+        <v>224</v>
       </c>
       <c r="E9" t="s">
-        <v>446</v>
+        <v>227</v>
       </c>
       <c r="F9" t="s">
-        <v>447</v>
+        <v>228</v>
       </c>
       <c r="G9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N9" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>448</v>
+        <v>229</v>
       </c>
       <c r="E10" t="s">
-        <v>449</v>
+        <v>230</v>
       </c>
       <c r="F10" t="s">
-        <v>450</v>
+        <v>231</v>
       </c>
       <c r="G10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N10" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>451</v>
+        <v>232</v>
       </c>
       <c r="E11" t="s">
-        <v>452</v>
+        <v>233</v>
       </c>
       <c r="F11" t="s">
-        <v>453</v>
+        <v>234</v>
       </c>
       <c r="G11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N11" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>454</v>
+        <v>235</v>
       </c>
       <c r="E12" t="s">
-        <v>455</v>
+        <v>236</v>
       </c>
       <c r="F12" t="s">
-        <v>456</v>
+        <v>237</v>
       </c>
       <c r="G12" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H12" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I12" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J12" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K12" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L12" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M12" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N12" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>454</v>
+        <v>235</v>
       </c>
       <c r="E13" t="s">
-        <v>457</v>
+        <v>238</v>
       </c>
       <c r="F13" t="s">
-        <v>458</v>
+        <v>239</v>
       </c>
       <c r="G13" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H13" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I13" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J13" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K13" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -5518,24 +4855,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="12.6640625"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="24.44140625"/>
-    <col bestFit="true" customWidth="true" max="4" min="4" width="25.5546875"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="34.88671875"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="26.6640625"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5579,312 +4916,312 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>459</v>
+        <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>460</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>461</v>
+        <v>242</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>462</v>
+        <v>243</v>
       </c>
       <c r="E3" t="s">
-        <v>463</v>
+        <v>244</v>
       </c>
       <c r="F3" t="s">
-        <v>464</v>
+        <v>245</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>465</v>
+        <v>246</v>
       </c>
       <c r="E4" t="s">
-        <v>466</v>
+        <v>247</v>
       </c>
       <c r="F4" t="s">
-        <v>467</v>
+        <v>248</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>468</v>
+        <v>249</v>
       </c>
       <c r="E5" t="s">
-        <v>469</v>
+        <v>250</v>
       </c>
       <c r="F5" t="s">
-        <v>470</v>
+        <v>251</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>471</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>472</v>
+        <v>253</v>
       </c>
       <c r="F6" t="s">
-        <v>473</v>
+        <v>254</v>
       </c>
       <c r="G6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>474</v>
+        <v>255</v>
       </c>
       <c r="E7" t="s">
-        <v>475</v>
+        <v>256</v>
       </c>
       <c r="F7" t="s">
-        <v>476</v>
+        <v>257</v>
       </c>
       <c r="G7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>477</v>
+        <v>258</v>
       </c>
       <c r="E8" t="s">
-        <v>478</v>
+        <v>259</v>
       </c>
       <c r="F8" t="s">
-        <v>479</v>
+        <v>260</v>
       </c>
       <c r="G8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -5895,12 +5232,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="14.6640625"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="44.77734375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5910,13 +5248,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -5944,180 +5282,180 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F2" t="s">
-        <v>482</v>
+        <v>89</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" t="s">
-        <v>483</v>
-      </c>
-      <c r="E3" t="s">
-        <v>484</v>
-      </c>
-      <c r="F3" t="s">
-        <v>485</v>
+        <v>91</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D4" t="s">
-        <v>486</v>
-      </c>
-      <c r="E4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F4" t="s">
-        <v>488</v>
+        <v>93</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>189</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D5" t="s">
-        <v>489</v>
-      </c>
-      <c r="E5" t="s">
-        <v>490</v>
-      </c>
-      <c r="F5" t="s">
-        <v>491</v>
+        <v>95</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>272</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -6128,24 +5466,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="13.109375"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="31.33203125"/>
-    <col bestFit="true" customWidth="true" max="4" min="4" width="24.6640625"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="36.5546875"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="31.21875"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6189,444 +5527,444 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>492</v>
+        <v>273</v>
       </c>
       <c r="E2" t="s">
-        <v>493</v>
+        <v>274</v>
       </c>
       <c r="F2" t="s">
-        <v>494</v>
+        <v>275</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>495</v>
+        <v>276</v>
       </c>
       <c r="E3" t="s">
-        <v>496</v>
+        <v>277</v>
       </c>
       <c r="F3" t="s">
-        <v>497</v>
+        <v>278</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>498</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
-        <v>499</v>
+        <v>280</v>
       </c>
       <c r="F4" t="s">
-        <v>500</v>
+        <v>281</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>208</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>501</v>
+        <v>282</v>
       </c>
       <c r="E5" t="s">
-        <v>502</v>
+        <v>283</v>
       </c>
       <c r="F5" t="s">
-        <v>503</v>
+        <v>284</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>213</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>504</v>
+        <v>285</v>
       </c>
       <c r="E6" t="s">
-        <v>505</v>
+        <v>286</v>
       </c>
       <c r="F6" t="s">
-        <v>506</v>
+        <v>287</v>
       </c>
       <c r="G6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>218</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>507</v>
+        <v>288</v>
       </c>
       <c r="E7" t="s">
-        <v>508</v>
+        <v>289</v>
       </c>
       <c r="F7" t="s">
-        <v>509</v>
+        <v>290</v>
       </c>
       <c r="G7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>224</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>510</v>
+        <v>291</v>
       </c>
       <c r="E8" t="s">
-        <v>511</v>
+        <v>292</v>
       </c>
       <c r="F8" t="s">
-        <v>512</v>
+        <v>293</v>
       </c>
       <c r="G8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N8" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>228</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>229</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>513</v>
+        <v>294</v>
       </c>
       <c r="E9" t="s">
-        <v>514</v>
+        <v>295</v>
       </c>
       <c r="F9" t="s">
-        <v>515</v>
+        <v>296</v>
       </c>
       <c r="G9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N9" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>233</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>516</v>
+        <v>297</v>
       </c>
       <c r="E10" t="s">
-        <v>517</v>
+        <v>298</v>
       </c>
       <c r="F10" t="s">
-        <v>518</v>
+        <v>299</v>
       </c>
       <c r="G10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N10" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>239</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>519</v>
+        <v>300</v>
       </c>
       <c r="E11" t="s">
-        <v>520</v>
+        <v>301</v>
       </c>
       <c r="F11" t="s">
-        <v>521</v>
+        <v>302</v>
       </c>
       <c r="G11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N11" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -6637,24 +5975,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="14"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="18.33203125"/>
-    <col bestFit="true" customWidth="true" max="4" min="4" width="20.21875"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="24.21875"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="28.5546875"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6698,268 +6036,268 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>243</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>522</v>
+        <v>303</v>
       </c>
       <c r="E2" t="s">
-        <v>523</v>
+        <v>304</v>
       </c>
       <c r="F2" t="s">
-        <v>524</v>
+        <v>305</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>248</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>525</v>
+        <v>306</v>
       </c>
       <c r="E3" t="s">
-        <v>526</v>
+        <v>307</v>
       </c>
       <c r="F3" t="s">
-        <v>527</v>
+        <v>308</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>253</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>528</v>
+        <v>309</v>
       </c>
       <c r="E4" t="s">
-        <v>529</v>
+        <v>310</v>
       </c>
       <c r="F4" t="s">
-        <v>530</v>
+        <v>311</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>258</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>531</v>
+        <v>312</v>
       </c>
       <c r="E5" t="s">
-        <v>532</v>
+        <v>313</v>
       </c>
       <c r="F5" t="s">
-        <v>533</v>
+        <v>314</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>261</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>262</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>525</v>
+        <v>306</v>
       </c>
       <c r="E6" t="s">
-        <v>534</v>
+        <v>315</v>
       </c>
       <c r="F6" t="s">
-        <v>535</v>
+        <v>316</v>
       </c>
       <c r="G6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>266</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>267</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>536</v>
+        <v>317</v>
       </c>
       <c r="E7" t="s">
-        <v>537</v>
+        <v>318</v>
       </c>
       <c r="F7" t="s">
-        <v>538</v>
+        <v>319</v>
       </c>
       <c r="G7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -6970,24 +6308,24 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="1" min="1" width="12.6640625"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="21.44140625"/>
-    <col bestFit="true" customWidth="true" max="4" min="4" width="19"/>
-    <col bestFit="true" customWidth="true" max="5" min="5" width="34.77734375"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="36.44140625"/>
-    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
-    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
-    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
-    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
-    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
-    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7031,752 +6369,752 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>272</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>539</v>
+        <v>320</v>
       </c>
       <c r="E2" t="s">
-        <v>540</v>
+        <v>321</v>
       </c>
       <c r="F2" t="s">
-        <v>541</v>
+        <v>322</v>
       </c>
       <c r="G2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>277</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>542</v>
+        <v>323</v>
       </c>
       <c r="E3" t="s">
-        <v>543</v>
+        <v>324</v>
       </c>
       <c r="F3" t="s">
-        <v>544</v>
+        <v>325</v>
       </c>
       <c r="G3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>280</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>281</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>545</v>
+        <v>326</v>
       </c>
       <c r="E4" t="s">
-        <v>546</v>
+        <v>327</v>
       </c>
       <c r="F4" t="s">
-        <v>547</v>
+        <v>328</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>548</v>
+        <v>329</v>
       </c>
       <c r="E5" t="s">
-        <v>549</v>
+        <v>330</v>
       </c>
       <c r="F5" t="s">
-        <v>550</v>
+        <v>331</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>288</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>551</v>
+        <v>332</v>
       </c>
       <c r="E6" t="s">
-        <v>552</v>
+        <v>333</v>
       </c>
       <c r="F6" t="s">
-        <v>553</v>
+        <v>334</v>
       </c>
       <c r="G6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M6" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>293</v>
+        <v>138</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>294</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>554</v>
+        <v>335</v>
       </c>
       <c r="E7" t="s">
-        <v>555</v>
+        <v>336</v>
       </c>
       <c r="F7" t="s">
-        <v>556</v>
+        <v>337</v>
       </c>
       <c r="G7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M7" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>297</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>298</v>
+        <v>141</v>
       </c>
       <c r="D8" t="s">
-        <v>557</v>
+        <v>338</v>
       </c>
       <c r="E8" t="s">
-        <v>558</v>
+        <v>339</v>
       </c>
       <c r="F8" t="s">
-        <v>559</v>
+        <v>340</v>
       </c>
       <c r="G8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M8" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N8" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>353</v>
+        <v>164</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>354</v>
+        <v>165</v>
       </c>
       <c r="D9" t="s">
-        <v>560</v>
+        <v>341</v>
       </c>
       <c r="E9" t="s">
-        <v>561</v>
+        <v>342</v>
       </c>
       <c r="F9" t="s">
-        <v>562</v>
+        <v>343</v>
       </c>
       <c r="G9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M9" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N9" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>359</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>360</v>
+        <v>168</v>
       </c>
       <c r="D10" t="s">
-        <v>563</v>
+        <v>344</v>
       </c>
       <c r="E10" t="s">
-        <v>564</v>
+        <v>345</v>
       </c>
       <c r="F10" t="s">
-        <v>565</v>
+        <v>346</v>
       </c>
       <c r="G10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M10" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N10" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>364</v>
+        <v>169</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>365</v>
+        <v>170</v>
       </c>
       <c r="D11" t="s">
-        <v>566</v>
+        <v>347</v>
       </c>
       <c r="E11" t="s">
-        <v>567</v>
+        <v>348</v>
       </c>
       <c r="F11" t="s">
-        <v>568</v>
+        <v>349</v>
       </c>
       <c r="G11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" t="s">
+        <v>166</v>
+      </c>
+      <c r="I11" t="s">
+        <v>166</v>
+      </c>
+      <c r="J11" t="s">
+        <v>166</v>
+      </c>
+      <c r="K11" t="s">
+        <v>166</v>
+      </c>
+      <c r="L11" t="s">
+        <v>166</v>
+      </c>
+      <c r="M11" t="s">
+        <v>166</v>
+      </c>
+      <c r="N11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F12" t="s">
+        <v>352</v>
+      </c>
+      <c r="G12" t="s">
+        <v>166</v>
+      </c>
+      <c r="H12" t="s">
+        <v>166</v>
+      </c>
+      <c r="I12" t="s">
+        <v>166</v>
+      </c>
+      <c r="J12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K12" t="s">
+        <v>166</v>
+      </c>
+      <c r="L12" t="s">
+        <v>166</v>
+      </c>
+      <c r="M12" t="s">
+        <v>166</v>
+      </c>
+      <c r="N12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" t="s">
+        <v>353</v>
+      </c>
+      <c r="E13" t="s">
+        <v>354</v>
+      </c>
+      <c r="F13" t="s">
+        <v>355</v>
+      </c>
+      <c r="G13" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" t="s">
+        <v>166</v>
+      </c>
+      <c r="I13" t="s">
+        <v>166</v>
+      </c>
+      <c r="J13" t="s">
+        <v>166</v>
+      </c>
+      <c r="K13" t="s">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s">
+        <v>166</v>
+      </c>
+      <c r="M13" t="s">
+        <v>166</v>
+      </c>
+      <c r="N13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" t="s">
+        <v>356</v>
+      </c>
+      <c r="E14" t="s">
+        <v>357</v>
+      </c>
+      <c r="F14" t="s">
         <v>358</v>
       </c>
-      <c r="H11" t="s">
-        <v>358</v>
-      </c>
-      <c r="I11" t="s">
-        <v>358</v>
-      </c>
-      <c r="J11" t="s">
-        <v>358</v>
-      </c>
-      <c r="K11" t="s">
-        <v>358</v>
-      </c>
-      <c r="L11" t="s">
-        <v>358</v>
-      </c>
-      <c r="M11" t="s">
-        <v>358</v>
-      </c>
-      <c r="N11" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>369</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>370</v>
-      </c>
-      <c r="D12" t="s">
-        <v>569</v>
-      </c>
-      <c r="E12" t="s">
-        <v>570</v>
-      </c>
-      <c r="F12" t="s">
-        <v>571</v>
-      </c>
-      <c r="G12" t="s">
-        <v>358</v>
-      </c>
-      <c r="H12" t="s">
-        <v>358</v>
-      </c>
-      <c r="I12" t="s">
-        <v>358</v>
-      </c>
-      <c r="J12" t="s">
-        <v>358</v>
-      </c>
-      <c r="K12" t="s">
-        <v>358</v>
-      </c>
-      <c r="L12" t="s">
-        <v>358</v>
-      </c>
-      <c r="M12" t="s">
-        <v>358</v>
-      </c>
-      <c r="N12" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>374</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>375</v>
-      </c>
-      <c r="D13" t="s">
-        <v>572</v>
-      </c>
-      <c r="E13" t="s">
-        <v>573</v>
-      </c>
-      <c r="F13" t="s">
-        <v>574</v>
-      </c>
-      <c r="G13" t="s">
-        <v>358</v>
-      </c>
-      <c r="H13" t="s">
-        <v>358</v>
-      </c>
-      <c r="I13" t="s">
-        <v>358</v>
-      </c>
-      <c r="J13" t="s">
-        <v>358</v>
-      </c>
-      <c r="K13" t="s">
-        <v>358</v>
-      </c>
-      <c r="L13" t="s">
-        <v>358</v>
-      </c>
-      <c r="M13" t="s">
-        <v>358</v>
-      </c>
-      <c r="N13" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>379</v>
-      </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>380</v>
-      </c>
-      <c r="D14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F14" t="s">
-        <v>577</v>
-      </c>
       <c r="G14" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H14" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I14" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J14" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K14" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>385</v>
+        <v>178</v>
       </c>
       <c r="D15" t="s">
-        <v>578</v>
+        <v>359</v>
       </c>
       <c r="E15" t="s">
-        <v>579</v>
+        <v>360</v>
       </c>
       <c r="F15" t="s">
-        <v>580</v>
+        <v>361</v>
       </c>
       <c r="G15" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H15" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I15" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J15" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K15" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M15" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N15" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>389</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>390</v>
+        <v>180</v>
       </c>
       <c r="D16" t="s">
-        <v>581</v>
+        <v>362</v>
       </c>
       <c r="E16" t="s">
-        <v>582</v>
+        <v>363</v>
       </c>
       <c r="F16" t="s">
-        <v>583</v>
+        <v>364</v>
       </c>
       <c r="G16" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H16" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I16" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J16" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K16" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L16" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M16" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N16" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>394</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>395</v>
+        <v>182</v>
       </c>
       <c r="D17" t="s">
-        <v>584</v>
+        <v>365</v>
       </c>
       <c r="E17" t="s">
-        <v>585</v>
+        <v>366</v>
       </c>
       <c r="F17" t="s">
-        <v>586</v>
+        <v>367</v>
       </c>
       <c r="G17" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H17" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I17" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J17" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K17" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L17" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M17" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N17" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>399</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>400</v>
+        <v>184</v>
       </c>
       <c r="D18" t="s">
-        <v>587</v>
+        <v>368</v>
       </c>
       <c r="E18" t="s">
-        <v>588</v>
+        <v>369</v>
       </c>
       <c r="F18" t="s">
-        <v>589</v>
+        <v>370</v>
       </c>
       <c r="G18" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="H18" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="I18" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="J18" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="K18" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="L18" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="M18" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="N18" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
